--- a/spa_forms/005_nail_studio_clean_beauty_interest_survey--spa_forms.xlsx
+++ b/spa_forms/005_nail_studio_clean_beauty_interest_survey--spa_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Survey Questions</t>
+          <t>Favorite Nail Polish Color</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,14 +548,10 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nail Polish Colors</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Select all that apply</t>
-        </is>
-      </c>
+          <t>Nail Polish Brand</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -565,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -575,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nail Polish Brands</t>
+          <t>Nail Polish Budget</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -588,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -598,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nail Polish Price Range</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -611,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -621,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nail Polish Brands</t>
+          <t>How Often Do You Get Your Nails Done</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -644,14 +640,10 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nail Polish Price Range</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Select only one option</t>
-        </is>
-      </c>
+          <t>How Often Do You Buy Nail Polish</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -661,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -671,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nail Polish Brands</t>
+          <t>Finish Preference</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -684,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -694,11 +686,57 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Importance of Chemical-Free Polish</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>page_9</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Purchase Preference</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>page_10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Number of Bottles at Home</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -715,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -743,102 +781,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>page_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>pastel_pink</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pink</t>
+          <t>Pastel Pink</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>page_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>deep_red</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Deep Red</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>page_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>purple</t>
+          <t>sparkly_purple</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Sparkly Purple</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>page_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>minty_fresh</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Minty Fresh</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>page_1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>brown</t>
+          <t>neutral_beige</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Neutral Beige</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>page_1_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -850,148 +888,148 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>sally_hansen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Sally Hansen</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>page_4_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>$0_-_$20</t>
+          <t>opi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>$0 - $20</t>
+          <t>OPI</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>page_4_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>$21_-_$40</t>
+          <t>essie</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>$21 - $40</t>
+          <t>Essie</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>page_4_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$41_-_$60</t>
+          <t>china_glaze</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>$41 - $60</t>
+          <t>China Glaze</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>page_4_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>more_than_$60</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>More than $60</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>page_5_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sally_hansen</t>
+          <t>$0_-_$20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sally Hansen</t>
+          <t>$0 - $20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>page_5_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>opi</t>
+          <t>$21_-_$40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OPI</t>
+          <t>$21 - $40</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>page_5_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>essie</t>
+          <t>$41_-_$60</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Essie</t>
+          <t>$41 - $60</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>page_5_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>china_glaze</t>
+          <t>more_than_$60</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Glaze</t>
+          <t>More than $60</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>deborah_lippman</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Deborah Lippman</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1020,63 +1058,63 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>page_6_choices</t>
+          <t>page_5_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>$10_-_$20</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>$10 - $20</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>page_6_choices</t>
+          <t>page_5_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>$21_-_$40</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>$21 - $40</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>page_6_choices</t>
+          <t>page_5_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>$41_-_$60</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>$41 - $60</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1126,301 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>more_than_$60</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>More than $60</t>
+          <t>Often</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>page_6_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>page_6_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>page_6_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>page_7_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>matte</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Matte</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>page_7_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>glossy</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Glossy</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>page_7_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>neither</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Neither</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>page_8_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>very_important</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Very Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>page_8_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>somewhat_important</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Somewhat Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>page_8_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>not_very_important</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Not Very Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>page_8_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>not_at_all_important</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Not at All Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>page_9_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>in_store</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>In Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>page_9_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>page_9_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>page_10_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>less_than_5</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Less than 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>page_10_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>5-10</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>5-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>page_10_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>11-20</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>11-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>page_10_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>more_than_20</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>More than 20</t>
         </is>
       </c>
     </row>
